--- a/EXCEL/Extra Practice /Test_Scores_Calc.xlsx
+++ b/EXCEL/Extra Practice /Test_Scores_Calc.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bethanyevittsair2/Documents/GitHub/BUS123-Solving-Business-Problems-with-Technology/EXCEL/Extra Practice /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3658FC26-01B1-144A-A9E3-1B36764C29EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B995F6-3940-434F-BD82-29765DC526C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3520" yWindow="3000" windowWidth="27640" windowHeight="16680" xr2:uid="{02F59F95-0823-6D40-9CC3-6EC04027227D}"/>
+    <workbookView xWindow="3520" yWindow="3000" windowWidth="33080" windowHeight="17680" xr2:uid="{02F59F95-0823-6D40-9CC3-6EC04027227D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Student Workbook" sheetId="3" r:id="rId1"/>
+    <sheet name="Function Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,9 +39,459 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="147">
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t># of Students</t>
+  </si>
+  <si>
+    <t>Average Grade</t>
+  </si>
+  <si>
+    <t>Bugs Bunny</t>
+  </si>
+  <si>
+    <t>Daffy Duck</t>
+  </si>
+  <si>
+    <t>Mickey Mouse</t>
+  </si>
+  <si>
+    <t>Minnie Mouse</t>
+  </si>
+  <si>
+    <t>SpongeBob SquarePants</t>
+  </si>
+  <si>
+    <t>Patrick Star</t>
+  </si>
+  <si>
+    <t>Lisa Simpson</t>
+  </si>
+  <si>
+    <t>Bart Simpson</t>
+  </si>
+  <si>
+    <t>Scooby-Doo</t>
+  </si>
+  <si>
+    <t>Shaggy Rogers</t>
+  </si>
+  <si>
+    <t>Velma Dinkley</t>
+  </si>
+  <si>
+    <t>Dora Explorer</t>
+  </si>
+  <si>
+    <t>Diego Márquez</t>
+  </si>
+  <si>
+    <t>Tom Cat</t>
+  </si>
+  <si>
+    <t>Jerry Mouse</t>
+  </si>
+  <si>
+    <t>Popeye Sailor</t>
+  </si>
+  <si>
+    <t>Olive Oyl</t>
+  </si>
+  <si>
+    <t>Fred Flintstone</t>
+  </si>
+  <si>
+    <t>Wilma Flintstone</t>
+  </si>
+  <si>
+    <t>George Jetson</t>
+  </si>
+  <si>
+    <t>Jane Jetson</t>
+  </si>
+  <si>
+    <t>Doraemon</t>
+  </si>
+  <si>
+    <t>Nobita Nobi</t>
+  </si>
+  <si>
+    <t>Garfield</t>
+  </si>
+  <si>
+    <t>Charlie Brown</t>
+  </si>
+  <si>
+    <t>Pass / Fail</t>
+  </si>
+  <si>
+    <t>Letter Grade</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Class Summary</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Function Practiced</t>
+  </si>
+  <si>
+    <t>COUNT</t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
+  </si>
+  <si>
+    <t>Highest Grade</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>Lowest Grade</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Total Grade Points</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>Passing Students</t>
+  </si>
+  <si>
+    <t>COUNTIF</t>
+  </si>
+  <si>
+    <t>Failing Students</t>
+  </si>
+  <si>
+    <t>Pass Rate</t>
+  </si>
+  <si>
+    <t>COUNTIF / COUNT</t>
+  </si>
+  <si>
+    <t>Top Student</t>
+  </si>
+  <si>
+    <t>INDEX / MATCH</t>
+  </si>
+  <si>
+    <t>Lowest Student</t>
+  </si>
+  <si>
+    <t>Student Practice</t>
+  </si>
+  <si>
+    <t>What to Do</t>
+  </si>
+  <si>
+    <t>Excel Skill</t>
+  </si>
+  <si>
+    <t>Step 1</t>
+  </si>
+  <si>
+    <t>Step 2</t>
+  </si>
+  <si>
+    <t>Change a grade in column B and watch outputs update</t>
+  </si>
+  <si>
+    <t>Cell references</t>
+  </si>
+  <si>
+    <t>Step 3</t>
+  </si>
+  <si>
+    <t>Summary functions</t>
+  </si>
+  <si>
+    <t>Step 4</t>
+  </si>
+  <si>
+    <t>Sort by Rank or Grade</t>
+  </si>
+  <si>
+    <t>Sorting data</t>
+  </si>
+  <si>
+    <t>Step 5</t>
+  </si>
+  <si>
+    <t>Try changing pass threshold from 60 to 70</t>
+  </si>
+  <si>
+    <t>Logic formulas</t>
+  </si>
+  <si>
+    <t>Basic Excel Function Practice — Student Grades</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Inputs Needed</t>
+  </si>
+  <si>
+    <t>Example Formula</t>
+  </si>
+  <si>
+    <t>Step-by-Step Instructions</t>
+  </si>
+  <si>
+    <t>What Result Means</t>
+  </si>
+  <si>
+    <t>Counts how many numeric grades exist.</t>
+  </si>
+  <si>
+    <t>A range of numeric cells, such as B4:B28.</t>
+  </si>
+  <si>
+    <t>1) Click H4. 2) Type =COUNT(. 3) Select grades B4:B28. 4) Close with ) and press Enter.</t>
+  </si>
+  <si>
+    <t>Shows the number of students with grades entered.</t>
+  </si>
+  <si>
+    <t>Finds the class average grade.</t>
+  </si>
+  <si>
+    <t>A range of numeric grade cells.</t>
+  </si>
+  <si>
+    <t>1) Click H5. 2) Type =AVERAGE(. 3) Select B4:B28. 4) Close the formula and press Enter.</t>
+  </si>
+  <si>
+    <t>Shows the typical score for the class.</t>
+  </si>
+  <si>
+    <t>Finds the highest grade.</t>
+  </si>
+  <si>
+    <t>1) Click H6. 2) Type =MAX(. 3) Select B4:B28. 4) Close with ) and press Enter.</t>
+  </si>
+  <si>
+    <t>Shows the best score in the class.</t>
+  </si>
+  <si>
+    <t>Finds the lowest grade.</t>
+  </si>
+  <si>
+    <t>1) Click H7. 2) Type =MIN(. 3) Select B4:B28. 4) Close with ) and press Enter.</t>
+  </si>
+  <si>
+    <t>Shows the lowest score in the class.</t>
+  </si>
+  <si>
+    <t>Adds all grades together.</t>
+  </si>
+  <si>
+    <t>1) Click H8. 2) Type =SUM(. 3) Select B4:B28. 4) Close the formula and press Enter.</t>
+  </si>
+  <si>
+    <t>Shows total grade points for all students.</t>
+  </si>
+  <si>
+    <t>Counts grades that match a rule.</t>
+  </si>
+  <si>
+    <t>A range plus a condition, such as &gt;=60 or &lt;60.</t>
+  </si>
+  <si>
+    <t>1) Click H9. 2) Type =COUNTIF(. 3) Select B4:B28. 4) Add comma. 5) Type the rule in quotes. 6) Press Enter.</t>
+  </si>
+  <si>
+    <t>Shows how many students meet the condition.</t>
+  </si>
+  <si>
+    <t>IF</t>
+  </si>
+  <si>
+    <t>Returns one result if a test is true and another if false.</t>
+  </si>
+  <si>
+    <t>A logical test, value if true, and value if false.</t>
+  </si>
+  <si>
+    <t>1) Click C4. 2) Test whether B4&gt;=60. 3) Add Pass for true. 4) Add Fail for false. 5) Copy down.</t>
+  </si>
+  <si>
+    <t>Labels each student as Pass or Fail.</t>
+  </si>
+  <si>
+    <t>Nested IF</t>
+  </si>
+  <si>
+    <t>Assigns letter grades from number grades.</t>
+  </si>
+  <si>
+    <t>Several logical tests ordered from highest to lowest.</t>
+  </si>
+  <si>
+    <t>1) Start with the highest grade rule. 2) Add the next IF inside the false result. 3) Continue until the final F. 4) Copy down.</t>
+  </si>
+  <si>
+    <t>Turns each number grade into A, B, C, D, or F.</t>
+  </si>
+  <si>
+    <t>RANK.EQ</t>
+  </si>
+  <si>
+    <t>Ranks students from highest grade to lowest.</t>
+  </si>
+  <si>
+    <t>One grade cell, the full grade range, and sort order 0 for highest first.</t>
+  </si>
+  <si>
+    <t>1) Click E4. 2) Select B4 as the number to rank. 3) Add the full grade range with $ signs. 4) Add 0. 5) Copy down.</t>
+  </si>
+  <si>
+    <t>Rank 1 is the highest grade.</t>
+  </si>
+  <si>
+    <t>INDEX</t>
+  </si>
+  <si>
+    <t>Returns a value from a list by position.</t>
+  </si>
+  <si>
+    <t>A list to return from and a position number.</t>
+  </si>
+  <si>
+    <t>1) Use INDEX to choose the student-name list. 2) Use MATCH to find the position of the top grade. 3) Return the student name.</t>
+  </si>
+  <si>
+    <t>Shows the name connected to the top grade.</t>
+  </si>
+  <si>
+    <t>MATCH</t>
+  </si>
+  <si>
+    <t>Finds the position of a value in a list.</t>
+  </si>
+  <si>
+    <t>A lookup value, a lookup range, and match type 0 for exact match.</t>
+  </si>
+  <si>
+    <t>1) Choose the value to find. 2) Select the range to search. 3) Use 0 for exact match. 4) Combine with INDEX to return a name.</t>
+  </si>
+  <si>
+    <t>Tells Excel where the matching grade appears.</t>
+  </si>
+  <si>
+    <t>Division / Percent</t>
+  </si>
+  <si>
+    <t>Calculates pass rate as passing students divided by total students.</t>
+  </si>
+  <si>
+    <t>A numerator, denominator, and percent format.</t>
+  </si>
+  <si>
+    <t>1) Count passing students. 2) Divide by total students. 3) Format the cell as Percentage.</t>
+  </si>
+  <si>
+    <t>Shows the share of students passing.</t>
+  </si>
+  <si>
+    <t>Helpful Reminders</t>
+  </si>
+  <si>
+    <t>Ranges are groups of cells, like B4:B28.</t>
+  </si>
+  <si>
+    <t>Text in formulas usually goes inside quotation marks, like "Pass".</t>
+  </si>
+  <si>
+    <t>Dollar signs lock a range when copying formulas, like $B$4:$B$28.</t>
+  </si>
+  <si>
+    <t>Press Enter after typing a formula, then check whether the result makes sense.</t>
+  </si>
+  <si>
+    <t>=COUNT(B4:B28)</t>
+  </si>
+  <si>
+    <t>=AVERAGE(B4:B28)</t>
+  </si>
+  <si>
+    <t>=MAX(B4:B28)</t>
+  </si>
+  <si>
+    <t>=MIN(B4:B28)</t>
+  </si>
+  <si>
+    <t>=SUM(B4:B28)</t>
+  </si>
+  <si>
+    <t>=COUNTIF(B4:B28,"&gt;=60")</t>
+  </si>
+  <si>
+    <t>=IF(B4&gt;=60,"Pass","Fail")</t>
+  </si>
+  <si>
+    <t>=IF(B4&gt;=90,"A",IF(B4&gt;=80,"B",IF(B4&gt;=70,"C",IF(B4&gt;=60,"D","F"))))</t>
+  </si>
+  <si>
+    <t>=RANK.EQ(B4,$B$4:$B$28,0)</t>
+  </si>
+  <si>
+    <t>=INDEX(A4:A28, MATCH(MAX(B4:B28),B4:B28,0))</t>
+  </si>
+  <si>
+    <t>=MATCH(MAX(B4:B28),B4:B28,0)</t>
+  </si>
+  <si>
+    <t>=COUNTIF(B4:B28,"&gt;=60")/COUNT(B4:B28)</t>
+  </si>
+  <si>
+    <t>Add formulas in C:E for each student</t>
+  </si>
+  <si>
+    <t>IF+ Nested IF + RANK</t>
+  </si>
+  <si>
+    <t>Calculate the results in column H</t>
+  </si>
+  <si>
+    <t>Passing Grade</t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
+  <si>
+    <t>Percentage Calc</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -48,16 +499,118 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF002060"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8B7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E3E5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B4B8A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDE7F6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6D5CA9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F0FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -65,18 +618,282 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFF8B7"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -403,11 +1220,860 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{A905A8F3-FEA3-4346-AC1A-258C7B0B9284}">
+  <we:reference id="wa200010215" version="2.0.0.0" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010215" version="2.0.0.0" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCF5DF40-617E-E242-A8BB-B1EBF574C37B}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E53007E2-A0FD-574E-950B-B86CF7E9AA41}">
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="25.6640625" customWidth="1"/>
+    <col min="9" max="9" width="24.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="38">
+        <v>94</v>
+      </c>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="43" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="19">
+        <v>67</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="19">
+        <v>88</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="8"/>
+      <c r="I6" s="44" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="19">
+        <v>76</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="8"/>
+      <c r="I7" s="44" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="19">
+        <v>59</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="19">
+        <v>41</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="8"/>
+      <c r="I9" s="44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="19">
+        <v>100</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="8"/>
+      <c r="I10" s="44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="19">
+        <v>72</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="19">
+        <v>83</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="19">
+        <v>55</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="19">
+        <v>98</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="19">
+        <v>63</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="19">
+        <v>79</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="19">
+        <v>36</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="19">
+        <v>92</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="19">
+        <v>48</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="19">
+        <v>81</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="20">
+        <v>69</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="20"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="20">
+        <v>87</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="20"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="20">
+        <v>52</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="20"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="20">
+        <v>74</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="20"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="20">
+        <v>91</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="20"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="20">
+        <v>28</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="20"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="20">
+        <v>44</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="20"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="21">
+        <v>96</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="21"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48A293EC-2152-5246-8B08-22373AACA096}">
+  <sheetPr>
+    <tabColor rgb="FF8064A2"/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.1640625" style="32" customWidth="1"/>
+    <col min="2" max="2" width="25" style="32" customWidth="1"/>
+    <col min="3" max="3" width="30" style="32" customWidth="1"/>
+    <col min="4" max="4" width="24.1640625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="36.6640625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="32" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+    </row>
+    <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A19:F19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>